--- a/src/ogrre_data_cleaning/processor_schemas/RRC Schema.xlsx
+++ b/src/ogrre_data_cleaning/processor_schemas/RRC Schema.xlsx
@@ -23,7 +23,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="213">
+  <si>
+    <t>Name</t>
+  </si>
   <si>
     <t>Processor Type</t>
   </si>
@@ -31,42 +34,54 @@
     <t>Google Processor Name</t>
   </si>
   <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Extractor</t>
+  </si>
+  <si>
     <t>OGRRE Document Type</t>
   </si>
   <si>
     <t>Page Order Sort</t>
   </si>
   <si>
+    <t>Follow-Up Processor</t>
+  </si>
+  <si>
     <t>Processor Name</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Model Enabled</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Model_Name_1 Fscore</t>
   </si>
   <si>
     <t>Model Name</t>
   </si>
   <si>
-    <t>Alias</t>
+    <t>Units</t>
   </si>
   <si>
     <t>F1 Score</t>
   </si>
   <si>
+    <t>Google Description Prompt</t>
+  </si>
+  <si>
     <t>Primary Model in Processor</t>
   </si>
   <si>
-    <t>Units</t>
+    <t>Google Data Type</t>
   </si>
   <si>
     <t>Training Documents</t>
   </si>
   <si>
-    <t>Google Description Prompt</t>
-  </si>
-  <si>
-    <t>Google Data Type</t>
-  </si>
-  <si>
     <t>Occurrence</t>
   </si>
   <si>
@@ -100,7 +115,7 @@
     <t>Field Specific Notes</t>
   </si>
   <si>
-    <t>Model Enabled</t>
+    <t>Classifier</t>
   </si>
   <si>
     <t>Fscores</t>
@@ -112,24 +127,9 @@
     <t>Texas_RRC_Splitter</t>
   </si>
   <si>
-    <t>Full Name</t>
-  </si>
-  <si>
     <t>V1</t>
   </si>
   <si>
-    <t>Classifier</t>
-  </si>
-  <si>
-    <t>Extractor</t>
-  </si>
-  <si>
-    <t>Follow-Up Processor</t>
-  </si>
-  <si>
-    <t>Model_Name_1 Fscore</t>
-  </si>
-  <si>
     <t>Custom</t>
   </si>
   <si>
@@ -169,60 +169,72 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Deliveries_1-B</t>
+  </si>
+  <si>
+    <t>Deliveries_1-B_Alt</t>
+  </si>
+  <si>
+    <t>Front_Page_1</t>
+  </si>
+  <si>
+    <t>Front_Page_1_Alt</t>
+  </si>
+  <si>
+    <t>Receipts_from_Leases_2</t>
+  </si>
+  <si>
+    <t>Receipts_from_Leases_2_Alt</t>
+  </si>
+  <si>
+    <t>Receipts_Other_Sources_1-A</t>
+  </si>
+  <si>
+    <t>Receipts_Other_Sources_1-A_Alt</t>
+  </si>
+  <si>
+    <t>Stock_on_Hand_3</t>
+  </si>
+  <si>
+    <t>Stock_on_Hand_3_Alt</t>
+  </si>
+  <si>
     <t>Google Data type</t>
   </si>
   <si>
-    <t>Deliveries_1-B</t>
-  </si>
-  <si>
-    <t>Deliveries_1-B_Alt</t>
-  </si>
-  <si>
     <t>Texas RRC T-1 Form - Page 1</t>
   </si>
   <si>
-    <t>Front_Page_1</t>
-  </si>
-  <si>
     <t>operator_name</t>
   </si>
   <si>
-    <t>Front_Page_1_Alt</t>
-  </si>
-  <si>
-    <t>Receipts_from_Leases_2</t>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>The operating company submitting the report.</t>
   </si>
   <si>
     <t>Plain text</t>
   </si>
   <si>
-    <t>Receipts_from_Leases_2_Alt</t>
-  </si>
-  <si>
-    <t>Receipts_Other_Sources_1-A</t>
-  </si>
-  <si>
     <t>Optional once</t>
   </si>
   <si>
-    <t>Receipts_Other_Sources_1-A_Alt</t>
-  </si>
-  <si>
-    <t>Stock_on_Hand_3</t>
-  </si>
-  <si>
     <t>str</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>Stock_on_Hand_3_Alt</t>
-  </si>
-  <si>
     <t>operator_month_year</t>
   </si>
   <si>
+    <t>Month/Year</t>
+  </si>
+  <si>
+    <t>The month and year for the report.</t>
+  </si>
+  <si>
     <t>date</t>
   </si>
   <si>
@@ -232,21 +244,57 @@
     <t>operator_address_street</t>
   </si>
   <si>
+    <t>Street or Box</t>
+  </si>
+  <si>
+    <t>Street or box address of the operator.</t>
+  </si>
+  <si>
     <t>operator_registration_no</t>
   </si>
   <si>
+    <t>Registration No.</t>
+  </si>
+  <si>
+    <t>Registration number.</t>
+  </si>
+  <si>
     <t>operator_p_5_no</t>
   </si>
   <si>
+    <t>P-5 No.</t>
+  </si>
+  <si>
+    <t>P-5 number.</t>
+  </si>
+  <si>
     <t>operator_address_city</t>
   </si>
   <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>City of the operator.</t>
+  </si>
+  <si>
     <t>operator_address_state</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>State of the operator.</t>
+  </si>
+  <si>
     <t>operator_address_zip_code</t>
   </si>
   <si>
+    <t>Zip Code</t>
+  </si>
+  <si>
+    <t>Zip Code of the operator.</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -256,9 +304,21 @@
     <t>operator_rrc_district</t>
   </si>
   <si>
+    <t>RRC District</t>
+  </si>
+  <si>
+    <t>Railroad Commission (RRC) District.</t>
+  </si>
+  <si>
     <t>operator_corrected_report</t>
   </si>
   <si>
+    <t>Corrected Report</t>
+  </si>
+  <si>
+    <t>Indicates if the report is a corrected report.</t>
+  </si>
+  <si>
     <t>Checkbox</t>
   </si>
   <si>
@@ -271,6 +331,15 @@
     <t>balance_available_for_movement_beginning</t>
   </si>
   <si>
+    <t>1. Balance Available for Movement (Beginning of Month)</t>
+  </si>
+  <si>
+    <t>Barrels</t>
+  </si>
+  <si>
+    <t>1. Balance Available for Movement (Beginning of Month) in barrels.</t>
+  </si>
+  <si>
     <t>Number</t>
   </si>
   <si>
@@ -283,24 +352,66 @@
     <t>balance_frozen_stock</t>
   </si>
   <si>
+    <t>2. Frozen Stock</t>
+  </si>
+  <si>
+    <t>2. Frozen Stock in barrels.</t>
+  </si>
+  <si>
     <t>balance_liquid_hydrocarbons_in_line</t>
   </si>
   <si>
+    <t>3. Liquid Hydrocarbons in Line</t>
+  </si>
+  <si>
+    <t>3. Liquid Hydrocarbons in Line in barrels.</t>
+  </si>
+  <si>
     <t>balance_total_stock_beginning</t>
   </si>
   <si>
+    <t>4. Total Stock (Beginning of Month)</t>
+  </si>
+  <si>
+    <t>4. Total Stock (Beginning of Month) in barrels.</t>
+  </si>
+  <si>
     <t>leases_receipts_crude</t>
   </si>
   <si>
+    <t>5. Receipts from Leases (Crude)</t>
+  </si>
+  <si>
+    <t>5. Receipts from Leases (Crude) in barrels.</t>
+  </si>
+  <si>
     <t>leases_receipts_condensate</t>
   </si>
   <si>
+    <t>6. Receipts from Leases (Condensate on Form PR)</t>
+  </si>
+  <si>
+    <t>6. Receipts from Leases (Condensate on Form PR) in barrels.</t>
+  </si>
+  <si>
     <t>leases_receipts_total</t>
   </si>
   <si>
+    <t>7. Receipts from Leases (Total)</t>
+  </si>
+  <si>
+    <t>7. Total Receipts from Leases in barrels.</t>
+  </si>
+  <si>
     <t>receipt_from_other_source</t>
   </si>
   <si>
+    <t>Receipt from Other Source</t>
+  </si>
+  <si>
+    <t>Rows details receipts from other sources.</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -313,82 +424,244 @@
     <t>receipt_from_other_source::received_from</t>
   </si>
   <si>
+    <t>8. Received From</t>
+  </si>
+  <si>
+    <t>8. Received from entity name.</t>
+  </si>
+  <si>
     <t>receipt_from_other_source::facility_name</t>
   </si>
   <si>
+    <t>9. Facility Name</t>
+  </si>
+  <si>
+    <t>9. Facility Name.</t>
+  </si>
+  <si>
     <t>receipt_from_other_source::rrc_identifier</t>
   </si>
   <si>
+    <t>10. RRC Identifier</t>
+  </si>
+  <si>
+    <t>10. RRC Identifier.</t>
+  </si>
+  <si>
     <t>receipt_from_other_source::actual_receipts</t>
   </si>
   <si>
+    <t>11. Actual Receipts</t>
+  </si>
+  <si>
+    <t>11. Actual Receipts in barrels.</t>
+  </si>
+  <si>
     <t>sources_receipts_total</t>
   </si>
   <si>
+    <t>12. Receipts from Other Sources (Total)</t>
+  </si>
+  <si>
+    <t>12. Total of receipts from other sources in barrels.</t>
+  </si>
+  <si>
     <t>sources_receipts_total_all</t>
   </si>
   <si>
+    <t>13. Receipts from Other Sources (Total All Receipts)</t>
+  </si>
+  <si>
+    <t>13. Total All Receipts in barrels.</t>
+  </si>
+  <si>
     <t>sources_stock_first_period_plus_receipts</t>
   </si>
   <si>
+    <t>14. Stock First of Period Plus Receipts</t>
+  </si>
+  <si>
+    <t>14. Stock First of Period Plus Receipts in barrels.</t>
+  </si>
+  <si>
     <t>delivery</t>
   </si>
   <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>Rows detailing deliveries.</t>
+  </si>
+  <si>
     <t>delivery::delivered_to</t>
   </si>
   <si>
+    <t>15. Delivered To</t>
+  </si>
+  <si>
+    <t>15. Delivered To entity name.</t>
+  </si>
+  <si>
     <t>delivery::facility_name</t>
   </si>
   <si>
+    <t>16. Facility Name</t>
+  </si>
+  <si>
+    <t>16. Facility Name.</t>
+  </si>
+  <si>
     <t>delivery::rrc_identifier</t>
   </si>
   <si>
+    <t>17. RRC Identifier</t>
+  </si>
+  <si>
+    <t>17. RRC Identifier.</t>
+  </si>
+  <si>
     <t>delivery::actual_deliveries</t>
   </si>
   <si>
+    <t>18. Actual Deliveries</t>
+  </si>
+  <si>
+    <t>18. Actual Deliveries in barrels.</t>
+  </si>
+  <si>
     <t>deliveries_total</t>
   </si>
   <si>
+    <t>19. Total</t>
+  </si>
+  <si>
+    <t>19. Total of actual deliveries in barrels.</t>
+  </si>
+  <si>
     <t>deliveries_overage</t>
   </si>
   <si>
+    <t>20. Overage</t>
+  </si>
+  <si>
+    <t>20. Overage in barrels.</t>
+  </si>
+  <si>
     <t>deliveries_shortage</t>
   </si>
   <si>
+    <t>21. Shortage</t>
+  </si>
+  <si>
+    <t>21. Shortage in barrels.</t>
+  </si>
+  <si>
     <t>deliveries_total_deliveries</t>
   </si>
   <si>
+    <t>22. Total Deliveries</t>
+  </si>
+  <si>
+    <t>22. Total Deliveries in barrels.</t>
+  </si>
+  <si>
     <t>stock_total_end_of_month</t>
   </si>
   <si>
+    <t>23. Total Stock End of Month (Detail on Page 3)</t>
+  </si>
+  <si>
+    <t>23. Total Stock End of Month in barrels.</t>
+  </si>
+  <si>
     <t>stock_frozen</t>
   </si>
   <si>
+    <t>24. Frozen Stock</t>
+  </si>
+  <si>
+    <t>24. Frozen Stock in barrels.</t>
+  </si>
+  <si>
     <t>stock_liquid_hydrocarbons_in_line</t>
   </si>
   <si>
+    <t>25. Liquid Hydrocarbons in Line</t>
+  </si>
+  <si>
+    <t>25. Liquid Hydrocarbons in Line in barrels.</t>
+  </si>
+  <si>
     <t>stock_balance_available_for_movement</t>
   </si>
   <si>
+    <t>26. Balance Available for Movement (End of Month)</t>
+  </si>
+  <si>
+    <t>26. Balance Available for Movement (End of Month) in barrels.</t>
+  </si>
+  <si>
     <t>signature_name</t>
   </si>
   <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Name written for the signature.</t>
+  </si>
+  <si>
     <t>signature_date</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Date the report was signed.</t>
+  </si>
+  <si>
     <t>signature_title</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Title of the person signing the report.</t>
+  </si>
+  <si>
     <t>signature_telephone_area_code</t>
   </si>
   <si>
+    <t>Area Code</t>
+  </si>
+  <si>
+    <t>Area code of the telephone number for the person signing the report.</t>
+  </si>
+  <si>
     <t>signature_telephone_number</t>
   </si>
   <si>
+    <t>Telephone Number</t>
+  </si>
+  <si>
+    <t>Telephone number (excluding the area code) for the person signing the report.</t>
+  </si>
+  <si>
     <t>signature_email</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Email address of the person signing the report.</t>
+  </si>
+  <si>
     <t>date_received</t>
+  </si>
+  <si>
+    <t>Date Received</t>
+  </si>
+  <si>
+    <t>Date received from the 'Received RRC of Texas' stamp/rectangle. Blank if not present.</t>
   </si>
 </sst>
 </file>
@@ -408,15 +681,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <color theme="1"/>
@@ -470,57 +743,30 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -529,50 +775,71 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -832,185 +1099,185 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0.987</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14">
+        <v>92.0</v>
+      </c>
+      <c r="G2" s="14">
+        <v>23.0</v>
+      </c>
+      <c r="H2" s="15">
+        <v>46218.0</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.987</v>
-      </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11">
-        <v>92.0</v>
-      </c>
-      <c r="G2" s="11">
-        <v>23.0</v>
-      </c>
-      <c r="H2" s="12">
-        <v>46218.0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="17">
         <v>0.969</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="18">
         <v>100.0</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="18">
         <v>30.0</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="19">
         <v>46226.0</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="20"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="20"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="20"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10">
       <c r="A10" s="23"/>
@@ -7675,298 +7942,298 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="G1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>26</v>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="22"/>
-      <c r="O6" s="5"/>
+      <c r="O6" s="6"/>
       <c r="P6" s="22"/>
     </row>
     <row r="7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="13"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
-      <c r="P7" s="13"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
       <c r="M9" s="26"/>
       <c r="N9" s="21"/>
       <c r="O9" s="21"/>
       <c r="P9" s="27"/>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="28"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="P11" s="13"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="P12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="P12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="P13" s="13"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
       <c r="N14" s="22"/>
-      <c r="P14" s="5"/>
+      <c r="P14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
       <c r="N15" s="21"/>
       <c r="O15" s="21"/>
-      <c r="P15" s="13"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="17">
-      <c r="C17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
+      <c r="C17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$15">
@@ -8008,73 +8275,73 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>34</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="B3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="B3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6">
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="12">
-      <c r="B12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13">
-      <c r="G13" s="13"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14">
-      <c r="B14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="16">
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$14">
@@ -8102,54 +8369,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>34</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3">
-      <c r="B3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="B3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="7">
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$F$5">
@@ -8177,240 +8444,240 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G4" s="6">
         <v>1.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+    <row r="5">
+      <c r="A5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="E5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G5" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
+    <row r="6">
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G7" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+    <row r="8">
+      <c r="A8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="F9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="5">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="G9" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G10" s="6">
+        <v>0.857</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+    <row r="12">
+      <c r="A12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G12" s="6">
         <v>1.0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.857</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
     <row r="13">
-      <c r="G13" s="13"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14">
-      <c r="B14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="16">
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$14">
@@ -8432,7 +8699,7 @@
     <col customWidth="1" min="1" max="1" width="9.0"/>
     <col customWidth="1" min="2" max="2" width="8.75"/>
     <col customWidth="1" min="3" max="3" width="7.5"/>
-    <col customWidth="1" min="4" max="4" width="21.63"/>
+    <col customWidth="1" min="4" max="4" width="33.63"/>
     <col customWidth="1" min="5" max="5" width="22.13"/>
     <col customWidth="1" min="6" max="8" width="16.63"/>
     <col customWidth="1" min="9" max="9" width="14.0"/>
@@ -8446,1658 +8713,1878 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="F1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>26</v>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>51</v>
+      <c r="B2" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="29">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="30"/>
+      <c r="D2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="32" t="s">
+      <c r="G2" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" s="32" t="s">
+      <c r="C3" s="33">
+        <v>2.0</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="5">
+      <c r="I3" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="16"/>
+      <c r="K3" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
+    <row r="4">
+      <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="34">
-        <v>2.0</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="36" t="s">
+      <c r="B4" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C4" s="29">
         <v>3.0</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="30"/>
+      <c r="D4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="32" t="s">
+      <c r="G4" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="32" t="s">
+      <c r="C5" s="33">
+        <v>4.0</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="5">
+      <c r="I5" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="16"/>
+      <c r="K5" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
+    <row r="6">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="34">
-        <v>4.0</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="36" t="s">
+      <c r="B6" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C6" s="29">
         <v>5.0</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="30"/>
+      <c r="D6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="F6" s="30"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="32" t="s">
+      <c r="G6" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="32" t="s">
+      <c r="C7" s="33">
+        <v>6.0</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="I7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="16"/>
+      <c r="K7" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="8">
+        <v>0.967</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="34">
-        <v>6.0</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="36" t="s">
+      <c r="B8" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="13">
-        <v>0.967</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C8" s="29">
         <v>7.0</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="30"/>
+      <c r="D8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="G8" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="6">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" s="32" t="s">
+      <c r="C9" s="33">
+        <v>8.0</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="5">
-        <v>0.983</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
+      <c r="I9" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="8">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="34">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="36" t="s">
+      <c r="B10" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="13">
-        <v>0.982</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C10" s="29">
         <v>9.0</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="30"/>
+      <c r="D10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="32" t="s">
+      <c r="G10" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="5">
+      <c r="C11" s="33">
+        <v>10.0</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="8">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6">
         <v>1.0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
+    <row r="13">
+      <c r="A13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="34">
-        <v>10.0</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="36" t="s">
+      <c r="B13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="13">
-        <v>0.182</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="C13" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="16"/>
+      <c r="K13" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="32" t="s">
+      <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5">
+      <c r="C14" s="6">
+        <v>13.0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6">
         <v>1.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
+    <row r="15">
+      <c r="A15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="13">
-        <v>12.0</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="36" t="s">
+      <c r="B15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13">
+      <c r="C15" s="8">
+        <v>14.0</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="16"/>
+      <c r="K15" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+    <row r="16">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="5">
-        <v>13.0</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="32" t="s">
+      <c r="B16" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L15" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C16" s="29">
         <v>15.0</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L16" s="32" t="s">
-        <v>84</v>
+      <c r="D16" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="31" t="s">
+        <v>107</v>
       </c>
       <c r="M16" s="29"/>
       <c r="N16" s="29"/>
       <c r="O16" s="29"/>
-      <c r="P16" s="5">
+      <c r="P16" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="13">
+      <c r="B17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="8">
         <v>16.0</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" s="36" t="s">
-        <v>84</v>
+      <c r="D17" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>107</v>
       </c>
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
       <c r="O17" s="21"/>
-      <c r="P17" s="13">
+      <c r="P17" s="8">
         <v>1.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>51</v>
+      <c r="B18" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C18" s="29">
         <v>17.0</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="32" t="s">
+      <c r="D18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L18" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
+      <c r="C19" s="33">
+        <v>18.0</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="27"/>
+      <c r="G19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J19" s="16"/>
+      <c r="K19" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="8">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="34">
-        <v>18.0</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="L19" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="13">
-        <v>0.979</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>51</v>
+      <c r="B20" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C20" s="29">
         <v>19.0</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="30"/>
+      <c r="D20" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="32" t="s">
+      <c r="G20" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="11"/>
+      <c r="K20" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="6">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L20" s="32" t="s">
+      <c r="C21" s="33">
+        <v>20.0</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="27"/>
+      <c r="G21" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="5">
-        <v>0.981</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="s">
+      <c r="I21" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="16"/>
+      <c r="K21" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="34">
-        <v>20.0</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="36" t="s">
+      <c r="B22" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C22" s="29">
         <v>21.0</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="30"/>
+      <c r="D22" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="F22" s="30"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="32" t="s">
+      <c r="G22" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="6">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J22" s="7"/>
-      <c r="K22" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="5">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="s">
+      <c r="C23" s="33">
+        <v>22.0</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="16"/>
+      <c r="K23" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="8">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="34">
-        <v>22.0</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I23" s="36" t="s">
+      <c r="B24" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L23" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="13">
-        <v>0.991</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C24" s="29">
         <v>23.0</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I24" s="32" t="s">
+      <c r="D24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L24" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="5">
+      <c r="C25" s="33">
+        <v>24.0</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="16"/>
+      <c r="K25" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="s">
+    <row r="26">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="34">
-        <v>24.0</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I25" s="36" t="s">
+      <c r="B26" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L25" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C26" s="29">
         <v>25.0</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I26" s="32" t="s">
+      <c r="D26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L26" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L26" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="5">
+      <c r="C27" s="8">
+        <v>26.0</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J27" s="16"/>
+      <c r="K27" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="6">
+        <v>27.0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="P28" s="6">
         <v>1.0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="s">
+    <row r="29">
+      <c r="A29" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="13">
-        <v>26.0</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="L27" s="36" t="s">
+      <c r="B29" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="8">
+        <v>28.0</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="P27" s="13">
-        <v>0.991</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+      <c r="I29" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="16"/>
+      <c r="K29" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N29" s="21"/>
+      <c r="P29" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="5">
-        <v>27.0</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="32" t="s">
+      <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L28" s="32" t="s">
+      <c r="C30" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="P28" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="13">
-        <v>28.0</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L29" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="N29" s="21"/>
-      <c r="P29" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="5">
-        <v>29.0</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L30" s="32" t="s">
-        <v>63</v>
+      <c r="I30" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="N30" s="22"/>
       <c r="O30" s="22"/>
-      <c r="P30" s="5">
+      <c r="P30" s="6">
         <v>0.976</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="13">
+      <c r="B31" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="8">
         <v>30.0</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" s="16"/>
+      <c r="K31" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I31" s="36" t="s">
+      <c r="L31" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L31" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="P31" s="13">
-        <v>0.984</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="5">
+      <c r="C32" s="6">
         <v>31.0</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="11"/>
+      <c r="K32" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L32" s="31" t="s">
         <v>107</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L32" s="32" t="s">
-        <v>84</v>
       </c>
       <c r="M32" s="28"/>
       <c r="N32" s="22"/>
       <c r="O32" s="22"/>
-      <c r="P32" s="5">
+      <c r="P32" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="13">
+      <c r="B33" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="8">
         <v>32.0</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I33" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M33" s="13"/>
+      <c r="D33" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J33" s="16"/>
+      <c r="K33" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L33" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M33" s="8"/>
       <c r="N33" s="21"/>
       <c r="O33" s="21"/>
-      <c r="P33" s="13">
+      <c r="P33" s="8">
         <v>1.0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="B34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="6">
         <v>33.0</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I34" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L34" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M34" s="5"/>
+      <c r="D34" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L34" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M34" s="6"/>
       <c r="N34" s="22"/>
       <c r="O34" s="22"/>
-      <c r="P34" s="5">
+      <c r="P34" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="B35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="8">
         <v>34.0</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I35" s="36" t="s">
+      <c r="D35" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J35" s="16"/>
+      <c r="K35" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L35" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M35" s="26"/>
+      <c r="P35" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L35" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M35" s="26"/>
-      <c r="P35" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C36" s="29">
         <v>35.0</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" s="32" t="s">
+      <c r="D36" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L36" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J36" s="7"/>
-      <c r="K36" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L36" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="5">
+      <c r="C37" s="33">
+        <v>36.0</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37" s="16"/>
+      <c r="K37" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L37" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="s">
+    <row r="38">
+      <c r="A38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="34">
-        <v>36.0</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I37" s="36" t="s">
+      <c r="B38" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L37" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C38" s="29">
         <v>37.0</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="I38" s="32" t="s">
+      <c r="D38" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="K38" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L38" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="L38" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="5">
+      <c r="C39" s="33">
+        <v>38.0</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I39" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39" s="16"/>
+      <c r="K39" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L39" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="8">
         <v>1.0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="s">
+    <row r="40">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="34">
-        <v>38.0</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I39" s="36" t="s">
+      <c r="B40" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="L39" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C40" s="29">
         <v>39.0</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="30"/>
+      <c r="D40" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>193</v>
+      </c>
       <c r="F40" s="30"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I40" s="32" t="s">
+      <c r="G40" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="K40" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L40" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J40" s="7"/>
-      <c r="K40" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L40" s="32" t="s">
+      <c r="C41" s="33">
+        <v>40.0</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" s="27"/>
+      <c r="G41" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="5">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="s">
+      <c r="I41" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J41" s="16"/>
+      <c r="K41" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="34">
-        <v>40.0</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I41" s="36" t="s">
+      <c r="B42" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="L41" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C42" s="29">
         <v>41.0</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" s="30"/>
+      <c r="D42" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="F42" s="30"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I42" s="32" t="s">
+      <c r="G42" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L42" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="6">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L42" s="32" t="s">
+      <c r="C43" s="33">
+        <v>42.0</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F43" s="27"/>
+      <c r="G43" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="H43" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="s">
+      <c r="I43" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J43" s="16"/>
+      <c r="K43" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L43" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="8">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="34">
-        <v>42.0</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" s="36" t="s">
+      <c r="B44" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="J43" s="14"/>
-      <c r="K43" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L43" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="13">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="C44" s="29">
         <v>43.0</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="30"/>
+      <c r="D44" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>205</v>
+      </c>
       <c r="F44" s="30"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I44" s="32" t="s">
+      <c r="G44" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="11"/>
+      <c r="K44" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L44" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="6">
+        <v>0.949</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J44" s="7"/>
-      <c r="K44" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L44" s="32" t="s">
+      <c r="C45" s="33">
+        <v>44.0</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" s="27"/>
+      <c r="G45" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="5">
-        <v>0.949</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="s">
+      <c r="I45" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="J45" s="16"/>
+      <c r="K45" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L45" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="34">
-        <v>44.0</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="I45" s="36" t="s">
+      <c r="B46" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J45" s="14"/>
-      <c r="K45" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L45" s="36" t="s">
+      <c r="C46" s="6">
+        <v>45.0</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="H46" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="M45" s="37"/>
-      <c r="N45" s="37"/>
-      <c r="O45" s="37"/>
-      <c r="P45" s="13">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="I46" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J46" s="7"/>
-      <c r="K46" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="L46" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="M46" s="5"/>
+      <c r="I46" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46" s="11"/>
+      <c r="K46" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="M46" s="6"/>
       <c r="N46" s="22"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5">
+      <c r="O46" s="6"/>
+      <c r="P46" s="6">
         <v>0.952</v>
       </c>
     </row>

--- a/src/ogrre_data_cleaning/processor_schemas/RRC Schema.xlsx
+++ b/src/ogrre_data_cleaning/processor_schemas/RRC Schema.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="306">
   <si>
     <t>Name</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Google Processor Name</t>
   </si>
   <si>
+    <t>Processor Type</t>
+  </si>
+  <si>
     <t>OGRRE Document Type</t>
   </si>
   <si>
@@ -49,21 +52,21 @@
     <t>Alias</t>
   </si>
   <si>
+    <t>Extractor</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Follow-Up Processor</t>
+  </si>
+  <si>
+    <t>Google Description Prompt</t>
+  </si>
+  <si>
     <t>Classifier</t>
   </si>
   <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Extractor</t>
-  </si>
-  <si>
-    <t>Follow-Up Processor</t>
-  </si>
-  <si>
-    <t>Google Description Prompt</t>
-  </si>
-  <si>
     <t>Model Enabled</t>
   </si>
   <si>
@@ -82,27 +85,24 @@
     <t>Database Data Type</t>
   </si>
   <si>
+    <t>Processor Name</t>
+  </si>
+  <si>
     <t>Cleaning Function</t>
   </si>
   <si>
+    <t>Model Name</t>
+  </si>
+  <si>
     <t>Accepted Range</t>
   </si>
   <si>
-    <t>Processor Type</t>
-  </si>
-  <si>
     <t>Field Specific Notes</t>
   </si>
   <si>
     <t>Fscores</t>
   </si>
   <si>
-    <t>Processor Name</t>
-  </si>
-  <si>
-    <t>Model Name</t>
-  </si>
-  <si>
     <t>F1 Score</t>
   </si>
   <si>
@@ -328,6 +328,12 @@
     <t>State of the operator.</t>
   </si>
   <si>
+    <t>operator_operator</t>
+  </si>
+  <si>
+    <t>Name of the operator.</t>
+  </si>
+  <si>
     <t>operator_address_zip_code</t>
   </si>
   <si>
@@ -352,6 +358,12 @@
     <t>Railroad Commission (RRC) District.</t>
   </si>
   <si>
+    <t>document_type</t>
+  </si>
+  <si>
+    <t>Type of doc. Either 1A or 1B.</t>
+  </si>
+  <si>
     <t>operator_corrected_report</t>
   </si>
   <si>
@@ -367,6 +379,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>Month and year of the report.</t>
+  </si>
+  <si>
     <t>clean_bool</t>
   </si>
   <si>
@@ -388,6 +403,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>operator_address</t>
+  </si>
+  <si>
     <t>string_to_float</t>
   </si>
   <si>
@@ -400,6 +418,9 @@
     <t>2. Frozen Stock in barrels.</t>
   </si>
   <si>
+    <t>City of the operator's address.</t>
+  </si>
+  <si>
     <t>balance_liquid_hydrocarbons_in_line</t>
   </si>
   <si>
@@ -409,10 +430,7 @@
     <t>3. Liquid Hydrocarbons in Line in barrels.</t>
   </si>
   <si>
-    <t>operator_operator</t>
-  </si>
-  <si>
-    <t>Name of the operator.</t>
+    <t>State of the operator's address.</t>
   </si>
   <si>
     <t>balance_total_stock_beginning</t>
@@ -424,34 +442,46 @@
     <t>4. Total Stock (Beginning of Month) in barrels.</t>
   </si>
   <si>
+    <t>Zip code of the operator's address.</t>
+  </si>
+  <si>
+    <t>lease_receipts</t>
+  </si>
+  <si>
     <t>leases_receipts_crude</t>
   </si>
   <si>
     <t>5. Receipts from Leases (Crude)</t>
   </si>
   <si>
-    <t>document_type</t>
+    <t>Table containing detail of receipts from leases.</t>
   </si>
   <si>
     <t>5. Receipts from Leases (Crude) in barrels.</t>
   </si>
   <si>
-    <t>Type of doc. Either 1A or 1B.</t>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Optional multiple</t>
   </si>
   <si>
     <t>leases_receipts_condensate</t>
   </si>
   <si>
+    <t>operator_p5_no</t>
+  </si>
+  <si>
     <t>6. Receipts from Leases (Condensate on Form PR)</t>
   </si>
   <si>
-    <t>Month and year of the report.</t>
-  </si>
-  <si>
     <t>6. Receipts from Leases (Condensate on Form PR) in barrels.</t>
   </si>
   <si>
-    <t>operator_address</t>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>RRC district.</t>
   </si>
   <si>
     <t>leases_receipts_total</t>
@@ -463,6 +493,18 @@
     <t>7. Total Receipts from Leases in barrels.</t>
   </si>
   <si>
+    <t>operator_sheet_no</t>
+  </si>
+  <si>
+    <t>lease_receipts::adjustments</t>
+  </si>
+  <si>
+    <t>Sheet number.</t>
+  </si>
+  <si>
+    <t>Barrels adjusted.</t>
+  </si>
+  <si>
     <t>receipt_from_other_source</t>
   </si>
   <si>
@@ -472,100 +514,127 @@
     <t>Rows details receipts from other sources.</t>
   </si>
   <si>
-    <t>Parent</t>
-  </si>
-  <si>
-    <t>City of the operator's address.</t>
-  </si>
-  <si>
-    <t>Optional multiple</t>
-  </si>
-  <si>
-    <t>Table</t>
+    <t>Indicates if this is a corrected report.</t>
+  </si>
+  <si>
+    <t>lease_receipts::commingle_permit_no</t>
+  </si>
+  <si>
+    <t>Commingle Permit Number.</t>
   </si>
   <si>
     <t>receipt_from_other_source::received_from</t>
   </si>
   <si>
-    <t>State of the operator's address.</t>
-  </si>
-  <si>
     <t>8. Received From</t>
   </si>
   <si>
     <t>8. Received from entity name.</t>
   </si>
   <si>
-    <t>Zip code of the operator's address.</t>
+    <t>lease_receipts::drilling_permit_no</t>
+  </si>
+  <si>
+    <t>delivery</t>
+  </si>
+  <si>
+    <t>Drilling Permit Number.</t>
+  </si>
+  <si>
+    <t>Table of deliveries.</t>
+  </si>
+  <si>
+    <t>lease_receipts::lease_field</t>
+  </si>
+  <si>
+    <t>Field name.</t>
   </si>
   <si>
     <t>receipt_from_other_source::facility_name</t>
   </si>
   <si>
+    <t>delivery::delivery_type</t>
+  </si>
+  <si>
     <t>9. Facility Name</t>
   </si>
   <si>
-    <t>lease_receipts</t>
+    <t>Type of delivery, e.g., 'Exports -' or 'Other -'.</t>
   </si>
   <si>
     <t>9. Facility Name.</t>
   </si>
   <si>
-    <t>Table containing detail of receipts from leases.</t>
-  </si>
-  <si>
-    <t>operator_p5_no</t>
+    <t>texas_rrc_clean_lease_field_or_operator</t>
+  </si>
+  <si>
+    <t>lease_receipts::lease_name</t>
+  </si>
+  <si>
+    <t>Lease name.</t>
+  </si>
+  <si>
+    <t>delivery::delivered_to</t>
+  </si>
+  <si>
+    <t>Entity the delivery was made to.</t>
+  </si>
+  <si>
+    <t>lease_receipts::lease_operator</t>
   </si>
   <si>
     <t>receipt_from_other_source::rrc_identifier</t>
   </si>
   <si>
-    <t>RRC district.</t>
+    <t>Operator name.</t>
+  </si>
+  <si>
+    <t>delivery::facility_address</t>
   </si>
   <si>
     <t>10. RRC Identifier</t>
   </si>
   <si>
-    <t>lease_receipts::adjustments</t>
+    <t>Address of the facility.</t>
   </si>
   <si>
     <t>10. RRC Identifier.</t>
   </si>
   <si>
-    <t>Barrels adjusted.</t>
-  </si>
-  <si>
-    <t>operator_sheet_no</t>
-  </si>
-  <si>
-    <t>Sheet number.</t>
+    <t>lease_receipts::oil_lease_no</t>
+  </si>
+  <si>
+    <t>Oil Lease Number.</t>
+  </si>
+  <si>
+    <t>delivery::facility_name</t>
+  </si>
+  <si>
+    <t>Name of the facility.</t>
   </si>
   <si>
     <t>receipt_from_other_source::actual_receipts</t>
   </si>
   <si>
-    <t>lease_receipts::commingle_permit_no</t>
-  </si>
-  <si>
     <t>11. Actual Receipts</t>
   </si>
   <si>
-    <t>Indicates if this is a corrected report.</t>
-  </si>
-  <si>
     <t>11. Actual Receipts in barrels.</t>
   </si>
   <si>
-    <t>Commingle Permit Number.</t>
-  </si>
-  <si>
-    <t>delivery</t>
-  </si>
-  <si>
-    <t>Table of deliveries.</t>
-  </si>
-  <si>
-    <t>lease_receipts::drilling_permit_no</t>
+    <t>lease_receipts::receipts</t>
+  </si>
+  <si>
+    <t>Barrels received.</t>
+  </si>
+  <si>
+    <t>delivery::rrc_identifier</t>
+  </si>
+  <si>
+    <t>RRC identifier for the facility.</t>
+  </si>
+  <si>
+    <t>lease_receipts::rrc_gas_id_no</t>
   </si>
   <si>
     <t>sources_receipts_total</t>
@@ -574,49 +643,37 @@
     <t>12. Receipts from Other Sources (Total)</t>
   </si>
   <si>
-    <t>Drilling Permit Number.</t>
+    <t>RRC Gas ID Number.</t>
   </si>
   <si>
     <t>12. Total of receipts from other sources in barrels.</t>
   </si>
   <si>
-    <t>delivery::delivery_type</t>
-  </si>
-  <si>
-    <t>Type of delivery, e.g., 'Exports -' or 'Other -'.</t>
-  </si>
-  <si>
-    <t>lease_receipts::lease_field</t>
-  </si>
-  <si>
-    <t>delivery::delivered_to</t>
+    <t>delivery::actual_deliveries</t>
+  </si>
+  <si>
+    <t>Actual deliveries amount.</t>
+  </si>
+  <si>
+    <t>Street or Box address of the operator.</t>
+  </si>
+  <si>
+    <t>receipts</t>
+  </si>
+  <si>
+    <t>receipts table in form 1A</t>
   </si>
   <si>
     <t>sources_receipts_total_all</t>
   </si>
   <si>
-    <t>Field name.</t>
-  </si>
-  <si>
-    <t>Entity the delivery was made to.</t>
-  </si>
-  <si>
     <t>13. Receipts from Other Sources (Total All Receipts)</t>
   </si>
   <si>
     <t>13. Total All Receipts in barrels.</t>
   </si>
   <si>
-    <t>delivery::facility_address</t>
-  </si>
-  <si>
-    <t>Address of the facility.</t>
-  </si>
-  <si>
-    <t>lease_receipts::lease_name</t>
-  </si>
-  <si>
-    <t>Lease name.</t>
+    <t>receipts::receipt_type</t>
   </si>
   <si>
     <t>sources_stock_first_period_plus_receipts</t>
@@ -625,25 +682,10 @@
     <t>14. Stock First of Period Plus Receipts</t>
   </si>
   <si>
-    <t>delivery::facility_name</t>
-  </si>
-  <si>
-    <t>Name of the facility.</t>
-  </si>
-  <si>
     <t>14. Stock First of Period Plus Receipts in barrels.</t>
   </si>
   <si>
-    <t>lease_receipts::lease_operator</t>
-  </si>
-  <si>
-    <t>delivery::rrc_identifier</t>
-  </si>
-  <si>
-    <t>Operator name.</t>
-  </si>
-  <si>
-    <t>RRC identifier for the facility.</t>
+    <t>receipts::received_from</t>
   </si>
   <si>
     <t>Delivery</t>
@@ -652,37 +694,22 @@
     <t>Rows detailing deliveries.</t>
   </si>
   <si>
-    <t>delivery::actual_deliveries</t>
-  </si>
-  <si>
-    <t>Actual deliveries amount.</t>
-  </si>
-  <si>
-    <t>lease_receipts::oil_lease_no</t>
-  </si>
-  <si>
-    <t>Oil Lease Number.</t>
-  </si>
-  <si>
-    <t>receipts</t>
+    <t>receipts::facility_address</t>
+  </si>
+  <si>
+    <t>receipts::facility_name</t>
   </si>
   <si>
     <t>15. Delivered To</t>
   </si>
   <si>
-    <t>receipts table in form 1A</t>
-  </si>
-  <si>
     <t>15. Delivered To entity name.</t>
   </si>
   <si>
-    <t>lease_receipts::receipts</t>
-  </si>
-  <si>
-    <t>receipts::receipt_type</t>
-  </si>
-  <si>
-    <t>Barrels received.</t>
+    <t>receipts::rrc_identifier</t>
+  </si>
+  <si>
+    <t>Month and Year of the report.</t>
   </si>
   <si>
     <t>16. Facility Name</t>
@@ -691,16 +718,7 @@
     <t>16. Facility Name.</t>
   </si>
   <si>
-    <t>receipts::received_from</t>
-  </si>
-  <si>
-    <t>lease_receipts::rrc_gas_id_no</t>
-  </si>
-  <si>
-    <t>RRC Gas ID Number.</t>
-  </si>
-  <si>
-    <t>receipts::facility_address</t>
+    <t>receipts::actual_receipts</t>
   </si>
   <si>
     <t>17. RRC Identifier</t>
@@ -709,13 +727,13 @@
     <t>17. RRC Identifier.</t>
   </si>
   <si>
-    <t>receipts::facility_name</t>
-  </si>
-  <si>
-    <t>Street or Box address of the operator.</t>
-  </si>
-  <si>
-    <t>receipts::rrc_identifier</t>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Total actual deliveries.</t>
+  </si>
+  <si>
+    <t>P-5 number of the operator.</t>
   </si>
   <si>
     <t>18. Actual Deliveries</t>
@@ -724,7 +742,7 @@
     <t>18. Actual Deliveries in barrels.</t>
   </si>
   <si>
-    <t>receipts::actual_receipts</t>
+    <t>Registration number of the operator.</t>
   </si>
   <si>
     <t>deliveries_total</t>
@@ -736,21 +754,24 @@
     <t>19. Total of actual deliveries in barrels.</t>
   </si>
   <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>Total actual deliveries.</t>
+    <t>RRC District number.</t>
   </si>
   <si>
     <t>deliveries_overage</t>
   </si>
   <si>
+    <t>Sheet number of the report.</t>
+  </si>
+  <si>
     <t>20. Overage</t>
   </si>
   <si>
     <t>20. Overage in barrels.</t>
   </si>
   <si>
+    <t>Total receipts and adjustments.</t>
+  </si>
+  <si>
     <t>deliveries_shortage</t>
   </si>
   <si>
@@ -769,9 +790,6 @@
     <t>22. Total Deliveries in barrels.</t>
   </si>
   <si>
-    <t>Month and Year of the report.</t>
-  </si>
-  <si>
     <t>stock_total_end_of_month</t>
   </si>
   <si>
@@ -787,18 +805,12 @@
     <t>24. Frozen Stock</t>
   </si>
   <si>
-    <t>P-5 number of the operator.</t>
-  </si>
-  <si>
     <t>24. Frozen Stock in barrels.</t>
   </si>
   <si>
     <t>stock_liquid_hydrocarbons_in_line</t>
   </si>
   <si>
-    <t>Registration number of the operator.</t>
-  </si>
-  <si>
     <t>25. Liquid Hydrocarbons in Line</t>
   </si>
   <si>
@@ -808,18 +820,12 @@
     <t>stock_balance_available_for_movement</t>
   </si>
   <si>
-    <t>RRC District number.</t>
-  </si>
-  <si>
     <t>26. Balance Available for Movement (End of Month)</t>
   </si>
   <si>
     <t>26. Balance Available for Movement (End of Month) in barrels.</t>
   </si>
   <si>
-    <t>Sheet number of the report.</t>
-  </si>
-  <si>
     <t>signature_name</t>
   </si>
   <si>
@@ -827,9 +833,6 @@
   </si>
   <si>
     <t>Name written for the signature.</t>
-  </si>
-  <si>
-    <t>Total receipts and adjustments.</t>
   </si>
   <si>
     <t>signature_date</t>
@@ -1049,32 +1052,32 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1085,6 +1088,7 @@
     <xf borderId="0" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1094,7 +1098,6 @@
     <xf borderId="0" fillId="4" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1448,51 +1451,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>0.988</v>
       </c>
       <c r="E2" s="14"/>
@@ -1505,65 +1508,65 @@
       <c r="H2" s="16">
         <v>46218.0</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>0.969</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <v>100.0</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="19">
         <v>30.0</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="20">
         <v>46226.0</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>0.897</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F4" s="15">
@@ -1575,65 +1578,65 @@
       <c r="H4" s="16">
         <v>46273.0</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <v>0.998</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <v>64.0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <v>18.0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <v>46274.0</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.936</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="15">
@@ -1645,41 +1648,41 @@
       <c r="H6" s="16">
         <v>46280.0</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="14"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="25"/>
@@ -8354,294 +8357,294 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="20"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="17"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="21"/>
-      <c r="O6" s="5"/>
+      <c r="O6" s="6"/>
       <c r="P6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="6"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="21"/>
       <c r="O8" s="21"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="22"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
       <c r="P9" s="23"/>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="24"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="P11" s="6"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="P11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="P12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="P12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="P13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="P13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
       <c r="N14" s="21"/>
-      <c r="P14" s="5"/>
+      <c r="P14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="17">
-      <c r="C17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="C17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$15">
@@ -8687,69 +8690,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3">
-      <c r="B3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6">
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="12">
-      <c r="B12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13">
-      <c r="G13" s="6"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14">
-      <c r="B14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="16">
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$14">
@@ -8781,50 +8784,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3">
-      <c r="B3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="7">
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="11"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$F$5">
@@ -8856,236 +8859,236 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>0.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>0.857</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>0.903</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="G13" s="6"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14">
-      <c r="B14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="16">
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$14">
@@ -9125,19 +9128,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
@@ -9146,25 +9149,25 @@
         <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>69</v>
@@ -9174,19 +9177,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="28">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F2" s="29"/>
@@ -9199,7 +9202,7 @@
       <c r="I2" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="30" t="s">
         <v>77</v>
       </c>
@@ -9209,25 +9212,25 @@
       <c r="M2" s="31"/>
       <c r="N2" s="31"/>
       <c r="O2" s="31"/>
-      <c r="P2" s="5">
+      <c r="P2" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q2" s="5"/>
+      <c r="Q2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C3" s="32">
         <v>2.0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="F3" s="23"/>
@@ -9240,7 +9243,7 @@
       <c r="I3" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="33" t="s">
         <v>82</v>
       </c>
@@ -9250,25 +9253,25 @@
       <c r="M3" s="34"/>
       <c r="N3" s="34"/>
       <c r="O3" s="34"/>
-      <c r="P3" s="6">
+      <c r="P3" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q3" s="6"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C4" s="28">
         <v>3.0</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F4" s="29"/>
@@ -9281,7 +9284,7 @@
       <c r="I4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="9"/>
       <c r="K4" s="30" t="s">
         <v>77</v>
       </c>
@@ -9291,25 +9294,25 @@
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="31"/>
-      <c r="P4" s="5">
+      <c r="P4" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C5" s="32">
         <v>4.0</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>88</v>
       </c>
       <c r="F5" s="23"/>
@@ -9322,7 +9325,7 @@
       <c r="I5" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="12"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="33" t="s">
         <v>77</v>
       </c>
@@ -9332,25 +9335,25 @@
       <c r="M5" s="34"/>
       <c r="N5" s="34"/>
       <c r="O5" s="34"/>
-      <c r="P5" s="6">
+      <c r="P5" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="28">
         <v>5.0</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>91</v>
       </c>
       <c r="F6" s="29"/>
@@ -9363,7 +9366,7 @@
       <c r="I6" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="9"/>
       <c r="K6" s="30" t="s">
         <v>77</v>
       </c>
@@ -9373,25 +9376,25 @@
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
       <c r="O6" s="31"/>
-      <c r="P6" s="5">
+      <c r="P6" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="32">
         <v>6.0</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F7" s="23"/>
@@ -9404,7 +9407,7 @@
       <c r="I7" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="33" t="s">
         <v>77</v>
       </c>
@@ -9414,25 +9417,25 @@
       <c r="M7" s="34"/>
       <c r="N7" s="34"/>
       <c r="O7" s="34"/>
-      <c r="P7" s="6">
+      <c r="P7" s="7">
         <v>0.967</v>
       </c>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="28">
         <v>7.0</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="29"/>
@@ -9445,7 +9448,7 @@
       <c r="I8" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="30" t="s">
         <v>77</v>
       </c>
@@ -9455,30 +9458,30 @@
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
       <c r="O8" s="31"/>
-      <c r="P8" s="5">
+      <c r="P8" s="6">
         <v>0.983</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="32">
         <v>8.0</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>100</v>
+      <c r="D9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>75</v>
@@ -9486,40 +9489,40 @@
       <c r="I9" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L9" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M9" s="34"/>
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
-      <c r="P9" s="6">
+      <c r="P9" s="7">
         <v>0.982</v>
       </c>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="7"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="28">
         <v>9.0</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>105</v>
+      <c r="D10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>75</v>
@@ -9527,7 +9530,7 @@
       <c r="I10" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="9"/>
       <c r="K10" s="30" t="s">
         <v>77</v>
       </c>
@@ -9537,245 +9540,245 @@
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
       <c r="O10" s="31"/>
-      <c r="P10" s="5">
+      <c r="P10" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C11" s="32">
         <v>10.0</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>108</v>
+      <c r="D11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="33" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I11" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L11" s="33" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M11" s="34"/>
       <c r="N11" s="34"/>
       <c r="O11" s="34"/>
-      <c r="P11" s="6">
+      <c r="P11" s="7">
         <v>0.182</v>
       </c>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>11.0</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>115</v>
+      <c r="D12" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I12" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="8"/>
+      <c r="J12" s="9"/>
       <c r="K12" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L12" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5">
+        <v>125</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>12.0</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="G13" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>122</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>117</v>
       </c>
       <c r="I13" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="13"/>
       <c r="K13" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L13" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6">
+        <v>125</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
         <v>13.0</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>115</v>
+      <c r="D14" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I14" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="9"/>
       <c r="K14" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L14" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5">
+        <v>125</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>14.0</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>115</v>
+      <c r="D15" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I15" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="13"/>
       <c r="K15" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L15" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6">
+        <v>125</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q15" s="6"/>
+      <c r="Q15" s="7"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="28">
         <v>15.0</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>115</v>
+      <c r="D16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H16" s="30" t="s">
         <v>75</v>
@@ -9783,42 +9786,42 @@
       <c r="I16" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="9"/>
       <c r="K16" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L16" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M16" s="28"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
-      <c r="P16" s="5">
+      <c r="P16" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>16.0</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>115</v>
+      <c r="D17" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H17" s="33" t="s">
         <v>75</v>
@@ -9826,42 +9829,42 @@
       <c r="I17" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="13"/>
       <c r="K17" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L17" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="6">
+        <v>125</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q17" s="6"/>
+      <c r="Q17" s="7"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="28">
         <v>17.0</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>115</v>
+      <c r="D18" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H18" s="30" t="s">
         <v>75</v>
@@ -9869,50 +9872,50 @@
       <c r="I18" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="9"/>
       <c r="K18" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L18" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M18" s="31"/>
       <c r="N18" s="31"/>
       <c r="O18" s="31"/>
-      <c r="P18" s="5">
+      <c r="P18" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="6"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="32">
         <v>18.0</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>145</v>
+      <c r="D19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="33" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I19" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="33" t="s">
         <v>149</v>
-      </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="33" t="s">
-        <v>150</v>
       </c>
       <c r="L19" s="33" t="s">
         <v>78</v>
@@ -9920,30 +9923,30 @@
       <c r="M19" s="34"/>
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
-      <c r="P19" s="6">
+      <c r="P19" s="7">
         <v>0.979</v>
       </c>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="28">
         <v>19.0</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>153</v>
+      <c r="D20" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="F20" s="29"/>
       <c r="G20" s="30" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H20" s="30" t="s">
         <v>75</v>
@@ -9951,7 +9954,7 @@
       <c r="I20" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J20" s="8"/>
+      <c r="J20" s="9"/>
       <c r="K20" s="30" t="s">
         <v>77</v>
       </c>
@@ -9961,30 +9964,30 @@
       <c r="M20" s="31"/>
       <c r="N20" s="31"/>
       <c r="O20" s="31"/>
-      <c r="P20" s="5">
+      <c r="P20" s="6">
         <v>0.981</v>
       </c>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="6"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C21" s="32">
         <v>20.0</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>157</v>
+      <c r="D21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="33" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>75</v>
@@ -9992,7 +9995,7 @@
       <c r="I21" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J21" s="12"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="33" t="s">
         <v>77</v>
       </c>
@@ -10002,30 +10005,30 @@
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
-      <c r="P21" s="6">
+      <c r="P21" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="7"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C22" s="28">
         <v>21.0</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>164</v>
+      <c r="D22" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="F22" s="29"/>
       <c r="G22" s="30" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="H22" s="30" t="s">
         <v>75</v>
@@ -10033,7 +10036,7 @@
       <c r="I22" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J22" s="8"/>
+      <c r="J22" s="9"/>
       <c r="K22" s="30" t="s">
         <v>77</v>
       </c>
@@ -10043,240 +10046,240 @@
       <c r="M22" s="31"/>
       <c r="N22" s="31"/>
       <c r="O22" s="31"/>
-      <c r="P22" s="5">
+      <c r="P22" s="6">
         <v>0.94</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="6"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C23" s="32">
         <v>22.0</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>115</v>
+      <c r="D23" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="H23" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I23" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="13"/>
       <c r="K23" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L23" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M23" s="34"/>
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
-      <c r="P23" s="6">
+      <c r="P23" s="7">
         <v>0.991</v>
       </c>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="7"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="28">
         <v>23.0</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>115</v>
+      <c r="D24" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I24" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J24" s="8"/>
+      <c r="J24" s="9"/>
       <c r="K24" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L24" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M24" s="31"/>
       <c r="N24" s="31"/>
       <c r="O24" s="31"/>
-      <c r="P24" s="5">
+      <c r="P24" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="6"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C25" s="32">
         <v>24.0</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>115</v>
+      <c r="D25" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="H25" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I25" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="13"/>
       <c r="K25" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L25" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M25" s="34"/>
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
-      <c r="P25" s="6">
+      <c r="P25" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q25" s="6"/>
+      <c r="Q25" s="7"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C26" s="28">
         <v>25.0</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>115</v>
+      <c r="D26" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I26" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J26" s="8"/>
+      <c r="J26" s="9"/>
       <c r="K26" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L26" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M26" s="31"/>
       <c r="N26" s="31"/>
       <c r="O26" s="31"/>
-      <c r="P26" s="5">
+      <c r="P26" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="6"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
         <v>26.0</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F27" s="6"/>
+      <c r="D27" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="7"/>
       <c r="G27" s="33" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H27" s="33" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I27" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="33" t="s">
         <v>149</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="33" t="s">
-        <v>150</v>
       </c>
       <c r="L27" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="7">
         <v>0.991</v>
       </c>
-      <c r="Q27" s="6"/>
+      <c r="Q27" s="7"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="6">
         <v>27.0</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F28" s="5"/>
+      <c r="D28" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="30" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="H28" s="30" t="s">
         <v>75</v>
@@ -10284,37 +10287,37 @@
       <c r="I28" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J28" s="8"/>
+      <c r="J28" s="9"/>
       <c r="K28" s="30" t="s">
         <v>77</v>
       </c>
       <c r="L28" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="6"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>28.0</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F29" s="6"/>
+      <c r="D29" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F29" s="7"/>
       <c r="G29" s="33" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="H29" s="33" t="s">
         <v>75</v>
@@ -10322,38 +10325,38 @@
       <c r="I29" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="13"/>
       <c r="K29" s="33" t="s">
         <v>77</v>
       </c>
       <c r="L29" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="N29" s="20"/>
-      <c r="P29" s="6">
+      <c r="N29" s="17"/>
+      <c r="P29" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q29" s="6"/>
+      <c r="Q29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="6">
         <v>29.0</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="F30" s="5"/>
+      <c r="D30" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="30" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H30" s="30" t="s">
         <v>75</v>
@@ -10361,7 +10364,7 @@
       <c r="I30" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J30" s="8"/>
+      <c r="J30" s="9"/>
       <c r="K30" s="30" t="s">
         <v>77</v>
       </c>
@@ -10370,412 +10373,412 @@
       </c>
       <c r="N30" s="21"/>
       <c r="O30" s="21"/>
-      <c r="P30" s="5">
+      <c r="P30" s="6">
         <v>0.976</v>
       </c>
-      <c r="Q30" s="5"/>
+      <c r="Q30" s="6"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>30.0</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>115</v>
+      <c r="D31" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I31" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="12"/>
+      <c r="J31" s="13"/>
       <c r="K31" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L31" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="P31" s="6">
+        <v>125</v>
+      </c>
+      <c r="P31" s="7">
         <v>0.984</v>
       </c>
-      <c r="Q31" s="6"/>
+      <c r="Q31" s="7"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="6">
         <v>31.0</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>115</v>
+      <c r="D32" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I32" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J32" s="8"/>
+      <c r="J32" s="9"/>
       <c r="K32" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L32" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M32" s="24"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21"/>
-      <c r="P32" s="5">
+      <c r="P32" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q32" s="5"/>
+      <c r="Q32" s="6"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>32.0</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>115</v>
+      <c r="D33" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H33" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I33" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J33" s="12"/>
+      <c r="J33" s="13"/>
       <c r="K33" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L33" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="M33" s="6"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="6">
+        <v>125</v>
+      </c>
+      <c r="M33" s="7"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q33" s="6"/>
+      <c r="Q33" s="7"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="6">
         <v>33.0</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>115</v>
+      <c r="D34" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H34" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I34" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J34" s="8"/>
+      <c r="J34" s="9"/>
       <c r="K34" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L34" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="M34" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="M34" s="6"/>
       <c r="N34" s="21"/>
       <c r="O34" s="21"/>
-      <c r="P34" s="5">
+      <c r="P34" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="6"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="7">
         <v>34.0</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>115</v>
+      <c r="D35" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I35" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="13"/>
       <c r="K35" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L35" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M35" s="22"/>
-      <c r="P35" s="6">
+      <c r="P35" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q35" s="6"/>
+      <c r="Q35" s="7"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="28">
         <v>35.0</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>115</v>
+      <c r="D36" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G36" s="30" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H36" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I36" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J36" s="8"/>
+      <c r="J36" s="9"/>
       <c r="K36" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L36" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
       <c r="O36" s="31"/>
-      <c r="P36" s="5">
+      <c r="P36" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="6"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C37" s="32">
         <v>36.0</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>115</v>
+      <c r="D37" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H37" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I37" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J37" s="12"/>
+      <c r="J37" s="13"/>
       <c r="K37" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L37" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M37" s="34"/>
       <c r="N37" s="34"/>
       <c r="O37" s="34"/>
-      <c r="P37" s="6">
+      <c r="P37" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q37" s="6"/>
+      <c r="Q37" s="7"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C38" s="28">
         <v>37.0</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>115</v>
+      <c r="D38" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G38" s="30" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I38" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J38" s="8"/>
+      <c r="J38" s="9"/>
       <c r="K38" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L38" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M38" s="31"/>
       <c r="N38" s="31"/>
       <c r="O38" s="31"/>
-      <c r="P38" s="5">
+      <c r="P38" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="6"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C39" s="32">
         <v>38.0</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>115</v>
+      <c r="D39" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H39" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I39" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J39" s="12"/>
+      <c r="J39" s="13"/>
       <c r="K39" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L39" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M39" s="34"/>
       <c r="N39" s="34"/>
       <c r="O39" s="34"/>
-      <c r="P39" s="6">
+      <c r="P39" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q39" s="6"/>
+      <c r="Q39" s="7"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C40" s="28">
         <v>39.0</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>264</v>
+      <c r="D40" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="F40" s="29"/>
       <c r="G40" s="30" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H40" s="30" t="s">
         <v>75</v>
@@ -10783,7 +10786,7 @@
       <c r="I40" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J40" s="8"/>
+      <c r="J40" s="9"/>
       <c r="K40" s="30" t="s">
         <v>77</v>
       </c>
@@ -10793,30 +10796,30 @@
       <c r="M40" s="31"/>
       <c r="N40" s="31"/>
       <c r="O40" s="31"/>
-      <c r="P40" s="5">
+      <c r="P40" s="6">
         <v>0.88</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="6"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C41" s="32">
         <v>40.0</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>268</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H41" s="33" t="s">
         <v>75</v>
@@ -10824,7 +10827,7 @@
       <c r="I41" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J41" s="12"/>
+      <c r="J41" s="13"/>
       <c r="K41" s="33" t="s">
         <v>82</v>
       </c>
@@ -10834,30 +10837,30 @@
       <c r="M41" s="34"/>
       <c r="N41" s="34"/>
       <c r="O41" s="34"/>
-      <c r="P41" s="6">
+      <c r="P41" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q41" s="6"/>
+      <c r="Q41" s="7"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="28">
         <v>41.0</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="D42" s="6" t="s">
         <v>271</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="F42" s="29"/>
       <c r="G42" s="30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H42" s="30" t="s">
         <v>75</v>
@@ -10865,7 +10868,7 @@
       <c r="I42" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J42" s="8"/>
+      <c r="J42" s="9"/>
       <c r="K42" s="30" t="s">
         <v>77</v>
       </c>
@@ -10875,30 +10878,30 @@
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
-      <c r="P42" s="5">
+      <c r="P42" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q42" s="5"/>
+      <c r="Q42" s="6"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C43" s="32">
         <v>42.0</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>274</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="F43" s="23"/>
       <c r="G43" s="33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H43" s="33" t="s">
         <v>75</v>
@@ -10906,7 +10909,7 @@
       <c r="I43" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J43" s="12"/>
+      <c r="J43" s="13"/>
       <c r="K43" s="33" t="s">
         <v>77</v>
       </c>
@@ -10916,30 +10919,30 @@
       <c r="M43" s="34"/>
       <c r="N43" s="34"/>
       <c r="O43" s="34"/>
-      <c r="P43" s="6">
+      <c r="P43" s="7">
         <v>0.667</v>
       </c>
-      <c r="Q43" s="6"/>
+      <c r="Q43" s="7"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C44" s="28">
         <v>43.0</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="D44" s="6" t="s">
         <v>277</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="F44" s="29"/>
       <c r="G44" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H44" s="30" t="s">
         <v>75</v>
@@ -10947,7 +10950,7 @@
       <c r="I44" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J44" s="8"/>
+      <c r="J44" s="9"/>
       <c r="K44" s="30" t="s">
         <v>77</v>
       </c>
@@ -10957,30 +10960,30 @@
       <c r="M44" s="31"/>
       <c r="N44" s="31"/>
       <c r="O44" s="31"/>
-      <c r="P44" s="5">
+      <c r="P44" s="6">
         <v>0.949</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="6"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C45" s="32">
         <v>44.0</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="D45" s="7" t="s">
         <v>280</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>281</v>
       </c>
       <c r="F45" s="23"/>
       <c r="G45" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H45" s="33" t="s">
         <v>75</v>
@@ -10988,7 +10991,7 @@
       <c r="I45" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J45" s="12"/>
+      <c r="J45" s="13"/>
       <c r="K45" s="33" t="s">
         <v>77</v>
       </c>
@@ -10998,30 +11001,30 @@
       <c r="M45" s="34"/>
       <c r="N45" s="34"/>
       <c r="O45" s="34"/>
-      <c r="P45" s="6">
+      <c r="P45" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q45" s="6"/>
+      <c r="Q45" s="7"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="6">
         <v>45.0</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E46" s="5" t="s">
+      <c r="D46" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="E46" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>75</v>
@@ -11029,20 +11032,20 @@
       <c r="I46" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J46" s="8"/>
+      <c r="J46" s="9"/>
       <c r="K46" s="30" t="s">
         <v>82</v>
       </c>
       <c r="L46" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="M46" s="5"/>
+      <c r="M46" s="6"/>
       <c r="N46" s="21"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5">
+      <c r="O46" s="6"/>
+      <c r="P46" s="6">
         <v>0.952</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$Q$46"/>
@@ -11092,49 +11095,49 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -11145,12 +11148,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="37"/>
       <c r="G2" s="35" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="H2" s="35" t="s">
         <v>75</v>
@@ -11177,12 +11180,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E3" s="40"/>
       <c r="F3" s="42"/>
       <c r="G3" s="40" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="H3" s="40" t="s">
         <v>75</v>
@@ -11214,7 +11217,7 @@
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H4" s="35" t="s">
         <v>75</v>
@@ -11243,7 +11246,7 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="42"/>
@@ -11280,7 +11283,7 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H6" s="35" t="s">
         <v>75</v>
@@ -11312,7 +11315,7 @@
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
       <c r="G7" s="40" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H7" s="40" t="s">
         <v>75</v>
@@ -11339,12 +11342,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
       <c r="G8" s="35" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="H8" s="35" t="s">
         <v>75</v>
@@ -11403,7 +11406,7 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E10" s="35"/>
       <c r="F10" s="37"/>
@@ -11435,12 +11438,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
       <c r="G11" s="40" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="H11" s="40" t="s">
         <v>75</v>
@@ -11467,12 +11470,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E12" s="35"/>
       <c r="F12" s="37"/>
       <c r="G12" s="35" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="H12" s="35" t="s">
         <v>75</v>
@@ -11499,24 +11502,24 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="40" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I13" s="40" t="s">
         <v>76</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L13" s="40" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M13" s="47"/>
       <c r="N13" s="43"/>
@@ -11533,21 +11536,21 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="37"/>
       <c r="G14" s="35" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I14" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="45" t="s">
         <v>149</v>
-      </c>
-      <c r="K14" s="45" t="s">
-        <v>150</v>
       </c>
       <c r="L14" s="37"/>
       <c r="M14" s="37"/>
@@ -11565,12 +11568,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
       <c r="G15" s="40" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H15" s="40" t="s">
         <v>75</v>
@@ -11597,12 +11600,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E16" s="35"/>
       <c r="F16" s="35"/>
       <c r="G16" s="35" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H16" s="35" t="s">
         <v>75</v>
@@ -11629,12 +11632,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
       <c r="G17" s="40" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H17" s="40" t="s">
         <v>75</v>
@@ -11661,12 +11664,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
       <c r="G18" s="35" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H18" s="35" t="s">
         <v>75</v>
@@ -11693,12 +11696,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
       <c r="G19" s="40" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H19" s="40" t="s">
         <v>75</v>
@@ -11725,24 +11728,24 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
       <c r="G20" s="35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I20" s="35" t="s">
         <v>76</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L20" s="45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M20" s="37"/>
       <c r="N20" s="37"/>
@@ -11759,21 +11762,21 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E21" s="42"/>
       <c r="F21" s="42"/>
       <c r="G21" s="40" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H21" s="40" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I21" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="K21" s="46" t="s">
         <v>149</v>
-      </c>
-      <c r="K21" s="46" t="s">
-        <v>150</v>
       </c>
       <c r="L21" s="42"/>
       <c r="M21" s="43"/>
@@ -11791,7 +11794,7 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="35"/>
@@ -11821,7 +11824,7 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
@@ -11851,7 +11854,7 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="35"/>
@@ -11879,7 +11882,7 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="40"/>
@@ -11909,7 +11912,7 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
@@ -11939,7 +11942,7 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
@@ -11954,7 +11957,7 @@
         <v>77</v>
       </c>
       <c r="L27" s="46" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
@@ -11971,24 +11974,24 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E28" s="37"/>
       <c r="F28" s="37"/>
       <c r="G28" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I28" s="35" t="s">
         <v>76</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L28" s="45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M28" s="38"/>
       <c r="N28" s="38"/>
@@ -11998,10 +12001,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="C30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$933">
@@ -12111,49 +12114,49 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -12164,21 +12167,21 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="37"/>
       <c r="G2" s="35" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I2" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="45" t="s">
         <v>149</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>150</v>
       </c>
       <c r="L2" s="37"/>
       <c r="M2" s="38"/>
@@ -12196,21 +12199,21 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>76</v>
       </c>
       <c r="K3" s="40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L3" s="42"/>
       <c r="M3" s="43"/>
@@ -12228,12 +12231,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="H4" s="35" t="s">
         <v>75</v>
@@ -12260,12 +12263,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H5" s="40" t="s">
         <v>75</v>
@@ -12292,12 +12295,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H6" s="35" t="s">
         <v>75</v>
@@ -12308,7 +12311,9 @@
       <c r="K6" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="37"/>
+      <c r="L6" s="45" t="s">
+        <v>178</v>
+      </c>
       <c r="M6" s="38"/>
       <c r="N6" s="38"/>
       <c r="O6" s="38"/>
@@ -12324,12 +12329,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
       <c r="G7" s="40" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="H7" s="40" t="s">
         <v>75</v>
@@ -12356,12 +12361,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
       <c r="G8" s="35" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H8" s="35" t="s">
         <v>75</v>
@@ -12372,7 +12377,9 @@
       <c r="K8" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="37"/>
+      <c r="L8" s="45" t="s">
+        <v>178</v>
+      </c>
       <c r="M8" s="38"/>
       <c r="N8" s="38"/>
       <c r="O8" s="38"/>
@@ -12388,12 +12395,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H9" s="40" t="s">
         <v>75</v>
@@ -12420,21 +12427,21 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="35" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>76</v>
       </c>
       <c r="K10" s="35" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L10" s="37"/>
       <c r="M10" s="38"/>
@@ -12452,12 +12459,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
       <c r="G11" s="40" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="H11" s="40" t="s">
         <v>75</v>
@@ -12484,12 +12491,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E12" s="35"/>
       <c r="F12" s="37"/>
       <c r="G12" s="35" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="H12" s="35" t="s">
         <v>75</v>
@@ -12521,7 +12528,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="40" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H13" s="40" t="s">
         <v>75</v>
@@ -12553,7 +12560,7 @@
       <c r="E14" s="35"/>
       <c r="F14" s="35"/>
       <c r="G14" s="35" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H14" s="35" t="s">
         <v>75</v>
@@ -12579,12 +12586,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
       <c r="G15" s="40" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="H15" s="40" t="s">
         <v>75</v>
@@ -12611,24 +12618,24 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E16" s="35"/>
       <c r="F16" s="35"/>
       <c r="G16" s="35" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H16" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I16" s="35" t="s">
         <v>76</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L16" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M16" s="35"/>
       <c r="N16" s="37"/>
@@ -12648,7 +12655,7 @@
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
       <c r="G17" s="40" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="H17" s="40" t="s">
         <v>75</v>
@@ -12675,12 +12682,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="E18" s="35"/>
       <c r="F18" s="37"/>
       <c r="G18" s="35" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="H18" s="35" t="s">
         <v>75</v>
@@ -12707,12 +12714,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E19" s="40"/>
       <c r="F19" s="42"/>
       <c r="G19" s="40" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="H19" s="40" t="s">
         <v>75</v>
@@ -12721,10 +12728,10 @@
         <v>76</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L19" s="40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M19" s="40"/>
       <c r="N19" s="43"/>
@@ -12746,7 +12753,7 @@
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
       <c r="G20" s="35" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="H20" s="35" t="s">
         <v>75</v>
@@ -12755,10 +12762,10 @@
         <v>76</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L20" s="35" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M20" s="35"/>
       <c r="N20" s="37"/>
@@ -12775,12 +12782,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E21" s="40"/>
       <c r="F21" s="40"/>
       <c r="G21" s="40" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="H21" s="40" t="s">
         <v>75</v>
@@ -12807,12 +12814,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="37"/>
       <c r="G22" s="35" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="H22" s="35" t="s">
         <v>75</v>
@@ -12821,10 +12828,10 @@
         <v>76</v>
       </c>
       <c r="K22" s="35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L22" s="35" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M22" s="35"/>
       <c r="N22" s="38"/>
@@ -12841,21 +12848,21 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
       <c r="G23" s="40" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="H23" s="40" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I23" s="40" t="s">
         <v>76</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L23" s="42"/>
       <c r="M23" s="43"/>
@@ -12942,60 +12949,60 @@
       <c r="P28" s="39"/>
     </row>
     <row r="30">
-      <c r="C30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="C30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$933"/>
   <mergeCells count="46">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I28:J28"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I7:J7"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
   </mergeCells>
   <conditionalFormatting sqref="M14">
     <cfRule type="notContainsBlanks" dxfId="1" priority="1">
@@ -13006,11 +13013,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K23">
       <formula1>"bool,date,float,int,str,Table"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L23">
-      <formula1>"clean_bool,clean_date,convert_hole_size_to_decimal,None,string_to_float,string_to_int"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I23">
       <formula1>"Optional once,Optional multiple"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L23">
+      <formula1>"clean_bool,clean_date,convert_hole_size_to_decimal,None,string_to_float,string_to_int,texas_rrc_clean_lease_field_or_operator"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H23">
       <formula1>"Plain text,Number,Currency,Money,Datetime,Address,Checkbox,Parent"</formula1>
@@ -13050,68 +13057,68 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="6">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="30" t="s">
         <v>74</v>
       </c>
@@ -13121,37 +13128,37 @@
       <c r="I2" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
+      <c r="L2" s="9"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="7">
         <v>2.0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="33" t="s">
         <v>81</v>
       </c>
@@ -13161,39 +13168,39 @@
       <c r="I3" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="33" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6" t="s">
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="6">
         <v>3.0</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="30" t="s">
         <v>86</v>
       </c>
@@ -13203,37 +13210,37 @@
       <c r="I4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="9"/>
       <c r="K4" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5" t="s">
+      <c r="L4" s="9"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="7">
         <v>4.0</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="33" t="s">
         <v>89</v>
       </c>
@@ -13243,37 +13250,37 @@
       <c r="I5" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="12"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6" t="s">
+      <c r="L5" s="13"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="6">
         <v>5.0</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="30" t="s">
         <v>92</v>
       </c>
@@ -13283,37 +13290,37 @@
       <c r="I6" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="9"/>
       <c r="K6" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="5"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="21"/>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="B7" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="7">
         <v>6.0</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="33" t="s">
         <v>95</v>
       </c>
@@ -13323,37 +13330,37 @@
       <c r="I7" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="6" t="s">
+      <c r="L7" s="13"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="6">
         <v>7.0</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="30" t="s">
         <v>98</v>
       </c>
@@ -13363,39 +13370,39 @@
       <c r="I8" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="5"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="21"/>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="7">
         <v>8.0</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="6"/>
+      <c r="D9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="7"/>
       <c r="G9" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>75</v>
@@ -13403,41 +13410,41 @@
       <c r="I9" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L9" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M9" s="22"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="6" t="s">
+      <c r="N9" s="17"/>
+      <c r="O9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C10" s="6">
         <v>9.0</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="5"/>
+      <c r="D10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>75</v>
@@ -13445,38 +13452,38 @@
       <c r="I10" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="9"/>
       <c r="K10" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L10" s="8"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="24"/>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="7">
         <v>10.0</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="E11" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="7"/>
       <c r="G11" s="33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>75</v>
@@ -13484,75 +13491,75 @@
       <c r="I11" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="O11" s="6" t="s">
+      <c r="L11" s="13"/>
+      <c r="O11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C12" s="6">
         <v>11.0</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="E12" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I12" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="O12" s="5" t="s">
+      <c r="L12" s="9"/>
+      <c r="O12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="6">
         <v>0.998</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" s="7">
         <v>12.0</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="E13" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>75</v>
@@ -13560,80 +13567,80 @@
       <c r="I13" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="13"/>
       <c r="K13" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L13" s="12"/>
-      <c r="O13" s="6" t="s">
+      <c r="L13" s="13"/>
+      <c r="O13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="7">
         <v>0.996</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" s="6">
         <v>13.0</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>115</v>
+      <c r="E14" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I14" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="9"/>
       <c r="K14" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L14" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N14" s="21"/>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="6">
         <v>1.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B15" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="7">
         <v>14.0</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="E15" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F15" s="7"/>
       <c r="G15" s="33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>75</v>
@@ -13641,38 +13648,38 @@
       <c r="I15" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="13"/>
       <c r="K15" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="6" t="s">
+      <c r="L15" s="13"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="B16" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="6">
         <v>15.0</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="E16" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H16" s="30" t="s">
         <v>75</v>
@@ -13680,153 +13687,153 @@
       <c r="I16" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="9"/>
       <c r="K16" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="8"/>
+      <c r="L16" s="9"/>
       <c r="M16" s="21"/>
       <c r="N16" s="21"/>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="6">
         <v>0.996</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B17" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="7">
         <v>16.0</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>115</v>
+      <c r="D17" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I17" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="13"/>
       <c r="K17" s="33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L17" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="7">
         <v>1.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21"/>
-      <c r="P18" s="5"/>
+      <c r="P18" s="6"/>
     </row>
     <row r="19">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="6"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
-      <c r="P20" s="5"/>
+      <c r="P20" s="6"/>
     </row>
     <row r="21">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="6"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="7"/>
     </row>
     <row r="22">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
       <c r="M22" s="21"/>
       <c r="N22" s="21"/>
       <c r="O22" s="21"/>
-      <c r="P22" s="5"/>
+      <c r="P22" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$22">
